--- a/Data/Home/Kitchen.Temperature.xlsx
+++ b/Data/Home/Kitchen.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:I189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709236498</v>
+        <v>1711833626</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709263452</v>
+        <v>1711863248</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709272039</v>
+        <v>1711871585</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709281415</v>
+        <v>1711899705</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709286748</v>
+        <v>1711915125</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +634,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709290676</v>
+        <v>1711943720</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709225224</v>
+        <v>1711952313</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -689,10 +700,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709247956</v>
+        <v>1711956628</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +733,15 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +760,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709256261</v>
+        <v>1711979615</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +774,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +793,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709266913</v>
+        <v>1711985202</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +803,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +826,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709274262</v>
+        <v>1712000798</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +836,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +859,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709280383</v>
+        <v>1712029246</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +873,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +892,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709285655</v>
+        <v>1712037758</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +902,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +925,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709333788</v>
+        <v>1712044021</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +935,15 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +962,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709347419</v>
+        <v>1712066490</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +976,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +995,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709361521</v>
+        <v>1712075438</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +1005,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1028,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709366236</v>
+        <v>1712086642</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1038,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1061,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709369716</v>
+        <v>1712115788</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1075,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1094,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709408376</v>
+        <v>1712124502</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1104,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1127,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709418662</v>
+        <v>1712131029</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1137,15 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1164,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709432769</v>
+        <v>1712146381</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1178,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1197,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709438030</v>
+        <v>1712155333</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1169,10 +1207,11 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1230,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709455129</v>
+        <v>1712172419</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1201,10 +1240,11 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1263,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709460508</v>
+        <v>1712187389</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1233,10 +1273,15 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1300,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709516774</v>
+        <v>1712193998</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1265,10 +1310,11 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1333,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709523705</v>
+        <v>1712200729</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1343,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1366,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709541233</v>
+        <v>1712209105</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1380,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1399,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709546212</v>
+        <v>1712214171</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1361,10 +1409,15 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1436,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709574730</v>
+        <v>1712235215</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1446,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1469,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709586586</v>
+        <v>1712247655</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1483,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1502,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709601717</v>
+        <v>1712259828</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1512,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1535,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709611807</v>
+        <v>1712288307</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1545,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1568,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709624165</v>
+        <v>1712292412</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1578,11 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1601,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709630133</v>
+        <v>1712298217</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1615,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1634,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709658294</v>
+        <v>1712299582</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1644,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1667,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709679936</v>
+        <v>1712305928</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1677,15 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1704,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709689058</v>
+        <v>1712321189</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1718,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1737,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709718393</v>
+        <v>1712336978</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1751,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1770,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709741160</v>
+        <v>1712352028</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1784,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1803,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709767292</v>
+        <v>1712381182</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1817,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1836,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709774873</v>
+        <v>1712389439</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1850,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1869,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709783366</v>
+        <v>1712403833</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1883,11 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1906,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709795702</v>
+        <v>1712410117</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1920,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1939,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709799506</v>
+        <v>1712415324</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1953,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1972,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709835108</v>
+        <v>1712432674</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1986,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2005,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709848970</v>
+        <v>1712450162</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +2015,15 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2042,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709859094</v>
+        <v>1712454278</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2052,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2075,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709866456</v>
+        <v>1712460349</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2085,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2108,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709880256</v>
+        <v>1712468681</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2122,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2141,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709885009</v>
+        <v>1712474445</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2065,10 +2151,15 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2178,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709920762</v>
+        <v>1712494161</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2188,11 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2211,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709939479</v>
+        <v>1712500735</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2225,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2244,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709949284</v>
+        <v>1712524467</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2161,10 +2254,11 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2277,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709957079</v>
+        <v>1712539968</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2193,10 +2287,15 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2314,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709967272</v>
+        <v>1712545348</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2324,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2347,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709977569</v>
+        <v>1712549540</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2361,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2380,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709982964</v>
+        <v>1712565071</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2390,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2413,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710023815</v>
+        <v>1712583872</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2427,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2446,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710033471</v>
+        <v>1712604743</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2353,10 +2456,11 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2479,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710042863</v>
+        <v>1712632456</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2489,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2512,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710055922</v>
+        <v>1712638299</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2526,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2545,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710060214</v>
+        <v>1712649528</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2555,15 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2582,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710093386</v>
+        <v>1712670451</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2481,10 +2592,11 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2615,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710108545</v>
+        <v>1712681889</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2629,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2648,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710120004</v>
+        <v>1712691516</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2658,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2681,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710131046</v>
+        <v>1712719870</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2691,11 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2714,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710144798</v>
+        <v>1712728384</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2728,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2747,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710148677</v>
+        <v>1712734178</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,10 +2757,15 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2784,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710186415</v>
+        <v>1712757071</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2794,11 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2817,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710199934</v>
+        <v>1712763613</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2831,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2850,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710216130</v>
+        <v>1712778485</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2737,10 +2860,11 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2883,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710239071</v>
+        <v>1712803617</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2897,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2916,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710268842</v>
+        <v>1712812165</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2801,10 +2926,11 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2949,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710279593</v>
+        <v>1712821011</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2833,10 +2959,15 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2986,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710297971</v>
+        <v>1712851471</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +3000,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3019,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710324353</v>
+        <v>1712857333</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3033,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3052,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710329037</v>
+        <v>1712865773</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3066,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3085,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710364742</v>
+        <v>1712890515</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3099,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3118,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710381627</v>
+        <v>1712899198</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3128,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3151,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710396892</v>
+        <v>1712903915</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3161,11 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3184,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710400658</v>
+        <v>1712909011</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3198,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3217,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710404349</v>
+        <v>1712912801</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3227,15 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3254,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710410220</v>
+        <v>1712925234</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3121,10 +3264,11 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3287,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710451860</v>
+        <v>1712940052</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3301,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3320,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710469512</v>
+        <v>1712956708</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3330,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3353,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710477690</v>
+        <v>1712986714</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3217,10 +3363,11 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3386,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710489231</v>
+        <v>1712994712</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3400,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3419,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710495158</v>
+        <v>1713020789</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3433,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3452,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710528688</v>
+        <v>1713037493</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3466,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3485,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710543939</v>
+        <v>1713051160</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3495,15 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3522,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710555628</v>
+        <v>1713056960</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3377,10 +3532,11 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3555,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710582069</v>
+        <v>1713062643</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3569,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3588,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710616734</v>
+        <v>1713066679</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3441,10 +3598,11 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3621,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710632035</v>
+        <v>1713077874</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3473,10 +3631,15 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3658,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710639126</v>
+        <v>1713098563</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3672,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3691,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710647367</v>
+        <v>1713111109</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3537,10 +3701,11 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3724,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710659883</v>
+        <v>1713127729</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3569,10 +3734,11 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3757,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710666235</v>
+        <v>1713157559</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3771,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3790,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710696225</v>
+        <v>1713164314</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3633,10 +3800,11 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3823,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710714456</v>
+        <v>1713182987</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3837,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3856,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710727414</v>
+        <v>1713205344</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3866,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3889,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710734912</v>
+        <v>1713212745</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3899,11 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3922,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710750803</v>
+        <v>1713238875</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3936,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3955,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710756204</v>
+        <v>1713251289</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3965,15 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3992,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710786244</v>
+        <v>1713276923</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3825,10 +4002,11 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4025,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710801123</v>
+        <v>1713284510</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +4039,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4058,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710813139</v>
+        <v>1713296860</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4068,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4091,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710821928</v>
+        <v>1713325051</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3921,10 +4101,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4124,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710834358</v>
+        <v>1713337092</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4138,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4157,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710840023</v>
+        <v>1713342943</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4167,15 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4194,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710868047</v>
+        <v>1713360245</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4204,11 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4227,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710889506</v>
+        <v>1713376708</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4241,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4260,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710898151</v>
+        <v>1713387846</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4081,10 +4270,11 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4293,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710926033</v>
+        <v>1713403577</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4303,15 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4330,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710930903</v>
+        <v>1713410074</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4344,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4363,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710954976</v>
+        <v>1713424722</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4377,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4396,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710959688</v>
+        <v>1713431381</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4209,10 +4406,11 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4429,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710972702</v>
+        <v>1713451451</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4443,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4462,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710988826</v>
+        <v>1713470230</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4273,10 +4472,11 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4495,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1711013275</v>
+        <v>1713498529</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4509,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4528,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1711020827</v>
+        <v>1713506829</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4337,10 +4538,11 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4561,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1711060531</v>
+        <v>1713511079</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4571,15 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4598,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1711071240</v>
+        <v>1713533814</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4612,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4631,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1711095016</v>
+        <v>1713539757</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4645,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4664,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1711101595</v>
+        <v>1713556643</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4678,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4697,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1711133639</v>
+        <v>1713574060</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4711,11 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4734,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1711141592</v>
+        <v>1713578391</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4748,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4767,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1711147929</v>
+        <v>1713584006</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4781,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4800,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1711159345</v>
+        <v>1713592381</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4814,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4833,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1711166972</v>
+        <v>1713598429</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4847,11 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4870,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1711178176</v>
+        <v>1713626115</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4884,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4903,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1711183767</v>
+        <v>1713630906</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4917,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4936,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1711188557</v>
+        <v>1713638906</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4950,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4969,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1711229799</v>
+        <v>1713649335</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4753,10 +4979,15 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +5006,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1711247031</v>
+        <v>1713657780</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +5016,11 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5039,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1711259358</v>
+        <v>1713667341</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4817,10 +5049,11 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5072,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1711271972</v>
+        <v>1713672421</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5086,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5105,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1711277232</v>
+        <v>1713680092</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4881,10 +5115,15 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5142,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1711302238</v>
+        <v>1713703173</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4913,10 +5152,11 @@
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5175,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1711321966</v>
+        <v>1713707173</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5189,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5208,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1711332238</v>
+        <v>1713725249</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4977,10 +5218,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5241,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1711345964</v>
+        <v>1713735647</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5009,10 +5251,15 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5278,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1711355260</v>
+        <v>1713744196</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5041,10 +5288,11 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5311,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1711361531</v>
+        <v>1713754215</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5325,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5344,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1711388832</v>
+        <v>1713759008</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5354,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5377,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1711399715</v>
+        <v>1713767905</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5137,10 +5387,15 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5414,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1711423745</v>
+        <v>1713790688</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5428,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5447,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1711429016</v>
+        <v>1713796306</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5201,10 +5457,11 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+          <t>Kitchen.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5480,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1711452117</v>
+        <v>1713814525</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5490,11 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5513,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1711457097</v>
+        <v>1713842191</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5527,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5546,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1711473675</v>
+        <v>1713850815</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5297,10 +5556,11 @@
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5579,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1711486630</v>
+        <v>1713857747</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5589,15 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5616,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1711514442</v>
+        <v>1713878828</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5630,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5649,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1711519662</v>
+        <v>1713891044</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5663,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5682,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1711529155</v>
+        <v>1713905626</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5425,10 +5692,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5715,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1711540899</v>
+        <v>1713934738</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5729,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5748,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1711549893</v>
+        <v>1713940066</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5489,10 +5758,11 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5781,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1711559996</v>
+        <v>1713958785</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5521,10 +5791,15 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5818,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1711563530</v>
+        <v>1713963432</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5553,10 +5828,11 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5851,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1711573190</v>
+        <v>1713967009</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5865,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5884,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1711596372</v>
+        <v>1713992238</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5617,10 +5894,11 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5917,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1711606203</v>
+        <v>1714009126</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +5927,15 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Comfortable</t>
+          <t>Kitchen.Temperature.state: ExcessivelyCold</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5954,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1711614678</v>
+        <v>1714014655</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5681,10 +5964,11 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Warm</t>
+          <t>Kitchen.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5987,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1711624658</v>
+        <v>1714018609</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +6001,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +6020,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1711636401</v>
+        <v>1714028347</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +6030,11 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Kitchen.Temperature.state: Cold</t>
+          <t>Kitchen.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6053,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711642262</v>
+        <v>1714053421</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +6067,753 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1714073742</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1714102071</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1714114606</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1714118874</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1714139355</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1714145283</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1714160044</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1714177973</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: ExcessivelyCold</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1714181899</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1714186391</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1714194734</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1714203701</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1714225631</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1714232150</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1714247515</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1714265037</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: ExcessivelyCold</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1714269288</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Cold</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1714275476</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1714283880</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1714290930</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: ExcessivelyHot</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1714313926</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Warm</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Temperature_Change</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1714323141</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Kitchen.Temperature.state: Comfortable</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
